--- a/artfynd/A 19601-2026 artfynd.xlsx
+++ b/artfynd/A 19601-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>61679349</v>
       </c>
       <c r="B2" t="n">
-        <v>97034</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470098.9262181881</v>
+        <v>470099</v>
       </c>
       <c r="R2" t="n">
-        <v>6968015.678315242</v>
+        <v>6968016</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2009-06-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -798,6 +783,228 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>61679356</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99863</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1866</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Åsstarr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carex pallidula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Harmaja</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hoverberget: Bergsbyn 1:6, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>470126</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6968124</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2009-06-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2009-06-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Detalj. 2 tuvor inom 2 m2 vid nedre hyggeshörn. Brant skogssluttning, minihygge. Ca 125 m öster om väg 574.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bengt Petterson, Stefan Ericsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>61679357</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99863</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1866</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Åsstarr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carex pallidula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Harmaja</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hoverberget: Bergsbyn 1:6, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>470123</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6968126</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2009-06-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2009-06-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Detalj. 1 tuva vid nedre hyggeshörn. Brant skogssluttning, minihygge. Ca 125 m öster om väg 574.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bengt Petterson, Stefan Ericsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19601-2026 artfynd.xlsx
+++ b/artfynd/A 19601-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61679349</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61679356</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61679357</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>